--- a/data/trans_bre/P16A_n_R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,35</t>
+          <t>0,37; 5,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,42</t>
+          <t>-2,56; 3,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,06</t>
+          <t>-0,92; 4,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,78</t>
+          <t>-0,47; 4,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,55; —</t>
+          <t>-57,22; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,48; 451,1</t>
+          <t>-73,04; 291,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 456,44</t>
+          <t>-41,29; 569,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 328,18</t>
+          <t>-20,1; 374,07</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,1</t>
+          <t>1,02; 4,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,52</t>
+          <t>-0,44; 5,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,03</t>
+          <t>0,14; 3,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,03</t>
+          <t>1,2; 6,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,02; 1019,71</t>
+          <t>35,91; 886,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 233,3</t>
+          <t>-14,26; 240,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 447,33</t>
+          <t>-5,36; 528,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 245,19</t>
+          <t>19,33; 270,13</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,99</t>
+          <t>-0,02; 3,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,3</t>
+          <t>-0,09; 3,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,12</t>
+          <t>3,04; 10,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,08; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,13; 188,97</t>
+          <t>32,05; 203,08</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,22</t>
+          <t>-0,03; 3,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,82</t>
+          <t>3,87; 9,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 8,03</t>
+          <t>2,13; 8,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,46</t>
+          <t>-3,54; 3,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,9; —</t>
+          <t>-33,11; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>112,03; 2325,53</t>
+          <t>118,95; 2131,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,56; 538,36</t>
+          <t>52,97; 599,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 84,98</t>
+          <t>-44,89; 82,38</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,06</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,69</t>
+          <t>4,28; 15,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,98</t>
+          <t>0,68; 7,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 8,94</t>
+          <t>-1,42; 9,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,97; 617,11</t>
+          <t>51,89; 560,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,09; —</t>
+          <t>1,85; 2371,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 187,05</t>
+          <t>-13,44; 209,22</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,29</t>
+          <t>-0,97; 2,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,94</t>
+          <t>-0,39; 4,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 7,43</t>
+          <t>0,63; 7,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 6,8</t>
+          <t>-1,38; 6,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,39; —</t>
+          <t>-67,16; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 587,29</t>
+          <t>4,99; 636,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 80,23</t>
+          <t>-10,42; 85,22</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,18</t>
+          <t>-1,71; 1,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,0</t>
+          <t>-0,33; 2,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,6</t>
+          <t>-1,45; 2,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 7,91</t>
+          <t>-0,11; 7,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 93,98</t>
+          <t>-57,47; 102,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 365,25</t>
+          <t>-22,52; 343,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 168,36</t>
+          <t>-40,52; 138,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 290,74</t>
+          <t>8,85; 278,61</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,16</t>
+          <t>-0,48; 3,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,0</t>
+          <t>2,29; 6,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,24</t>
+          <t>2,8; 6,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,24</t>
+          <t>4,28; 9,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 161,82</t>
+          <t>-15,83; 164,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>93,69; 999,09</t>
+          <t>104,77; 1153,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>146,53; 1541,42</t>
+          <t>197,05; 1840,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,91; 619,09</t>
+          <t>89,76; 531,71</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,81</t>
+          <t>0,42; 1,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,09</t>
+          <t>2,3; 4,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,51</t>
+          <t>1,83; 3,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,62</t>
+          <t>2,72; 5,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,91; 147,9</t>
+          <t>21,21; 149,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>97,03; 282,46</t>
+          <t>104,48; 277,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>91,56; 252,42</t>
+          <t>90,34; 261,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>56,87; 152,43</t>
+          <t>56,59; 153,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,16</t>
+          <t>0,43; 5,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,11</t>
+          <t>-2,47; 3,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,19</t>
+          <t>-1,0; 4,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,15</t>
+          <t>-0,56; 3,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,22; —</t>
+          <t>-31,61; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,04; 291,73</t>
+          <t>-67,4; 381,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 569,9</t>
+          <t>-44,22; 505,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 374,07</t>
+          <t>-24,68; 286,3</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>105,17%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,76</t>
+          <t>0,81; 4,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,8</t>
+          <t>-0,58; 5,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,96</t>
+          <t>-0,02; 3,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,35</t>
+          <t>1,04; 6,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,91; 886,68</t>
+          <t>22,54; 819,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 240,86</t>
+          <t>-17,4; 243,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 528,36</t>
+          <t>-16,24; 391,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,33; 270,13</t>
+          <t>16,08; 255,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>6,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,0</t>
+          <t>-1,49; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,36</t>
+          <t>-0,0; 3,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,34</t>
+          <t>-0,05; 3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 10,64</t>
+          <t>2,93; 10,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,05; 203,08</t>
+          <t>32,43; 197,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,43</t>
+          <t>-0,13; 3,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,62</t>
+          <t>3,98; 9,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,41</t>
+          <t>2,01; 8,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,46</t>
+          <t>-1,28; 4,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,11; —</t>
+          <t>-41,43; 1493,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>118,95; 2131,95</t>
+          <t>122,79; 2097,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,97; 599,44</t>
+          <t>35,22; 572,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 82,38</t>
+          <t>-18,4; 137,75</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>128,26%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,04; 4,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,24</t>
+          <t>4,6; 15,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,48</t>
+          <t>0,8; 7,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 9,32</t>
+          <t>3,85; 11,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,89; 560,53</t>
+          <t>54,54; 585,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2371,8</t>
+          <t>4,97; 1931,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 209,22</t>
+          <t>47,08; 288,56</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,25</t>
+          <t>-0,91; 2,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,02</t>
+          <t>-0,39; 3,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,38</t>
+          <t>0,33; 7,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,91</t>
+          <t>-0,77; 7,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,16; —</t>
+          <t>-67,06; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 636,6</t>
+          <t>-1,74; 618,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 85,22</t>
+          <t>-7,71; 87,14</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>143,77%</t>
+          <t>215,93%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,39</t>
+          <t>-1,8; 1,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,98</t>
+          <t>-0,34; 3,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,54</t>
+          <t>-1,37; 2,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 7,99</t>
+          <t>5,16; 9,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-57,47; 102,77</t>
+          <t>-58,38; 109,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 343,47</t>
+          <t>-22,64; 387,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 138,99</t>
+          <t>-41,11; 166,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,85; 278,61</t>
+          <t>104,67; 377,86</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>199,41%</t>
+          <t>110,15%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,26</t>
+          <t>-0,68; 3,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,1</t>
+          <t>2,34; 6,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,38</t>
+          <t>2,63; 6,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,92</t>
+          <t>2,66; 6,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 164,91</t>
+          <t>-23,65; 146,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>104,77; 1153,21</t>
+          <t>113,3; 1232,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>197,05; 1840,72</t>
+          <t>151,33; 1592,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>89,76; 531,71</t>
+          <t>46,54; 196,46</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>101,37%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,8</t>
+          <t>0,46; 1,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,08</t>
+          <t>2,31; 4,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,54</t>
+          <t>1,89; 3,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,72</t>
+          <t>3,82; 5,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,21; 149,55</t>
+          <t>22,95; 147,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>104,48; 277,36</t>
+          <t>103,59; 291,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,34; 261,09</t>
+          <t>89,32; 254,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>56,59; 153,74</t>
+          <t>71,61; 134,68</t>
         </is>
       </c>
     </row>
